--- a/supply_order_forms/007_retail_shelf_tester_unit_order_form--supply_order_forms.xlsx
+++ b/supply_order_forms/007_retail_shelf_tester_unit_order_form--supply_order_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E20"/>
+  <dimension ref="A1:E18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -525,13 +525,13 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>unit_type</t>
+          <t>Unit Type</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -543,18 +543,18 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>quantity</t>
+          <t>unit_quantity</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>quantity</t>
+          <t>Quantity</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -571,13 +571,13 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>unit_price</t>
+          <t>Unit Price</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -594,13 +594,13 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>order_date</t>
+          <t>Order Date</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -617,13 +617,13 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>tester_unit_name</t>
+          <t>Tester Unit Name</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -635,18 +635,18 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>tester_unit_number</t>
+          <t>unit_number</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>tester_unit_number</t>
+          <t>Unit Number</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -663,13 +663,13 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>customer_name</t>
+          <t>Customer Name</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -681,18 +681,18 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>customer_email</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>Email</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -704,18 +704,18 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>customer_phone</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>Phone</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -732,13 +732,13 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>shipping_address</t>
+          <t>Shipping Address</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -750,18 +750,18 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>city</t>
+          <t>customer_city</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>city</t>
+          <t>City</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -773,18 +773,18 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>state</t>
+          <t>customer_state</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>state</t>
+          <t>State</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -796,18 +796,18 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>country</t>
+          <t>customer_country</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>country</t>
+          <t>Country</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -819,12 +819,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>notes</t>
+          <t>customer_notes</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>notes</t>
+          <t>Notes</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -837,67 +837,21 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>unit_type</t>
+          <t>customer_notes_2</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>unit_type</t>
+          <t>Customer Notes</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>tester_unit_number</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>tester_unit_number</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>customer_name</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>customer_name</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -914,10 +868,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:C5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="21" customWidth="1" min="1" max="1"/>
     <col width="6" customWidth="1" min="2" max="2"/>
     <col width="7" customWidth="1" min="3" max="3"/>
   </cols>
@@ -976,7 +930,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>tester_unit_number_choices</t>
+          <t>unit_number_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -993,7 +947,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>tester_unit_number_choices</t>
+          <t>unit_number_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1002,74 +956,6 @@
         </is>
       </c>
       <c r="C5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>unit_type_choices</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>unit_type_choices</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>tester_unit_number_choices</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>tester_unit_number_choices</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
         <is>
           <t>No</t>
         </is>
